--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769407</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136769415</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136769416</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136769417</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769407</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136769415</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136769416</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136769417</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -1381,11 +1381,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -1503,11 +1499,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -1625,11 +1617,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>
@@ -1747,11 +1735,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storlångmyrbackarna, Mpd</t>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769407</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136769415</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>136769416</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136769417</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136769410</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136769408</v>
       </c>
       <c r="B4" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136769411</v>
       </c>
       <c r="B5" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136769414</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136769413</v>
       </c>
       <c r="B7" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136769407</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>136769415</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>136769416</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136769417</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 60779-2024 artfynd.xlsx
+++ b/artfynd/A 60779-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136769409</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>136769412</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
